--- a/artfynd/A 17216-2026 artfynd.xlsx
+++ b/artfynd/A 17216-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96673163</v>
+        <v>96673157</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578430.1237809489</v>
+        <v>578390</v>
       </c>
       <c r="R2" t="n">
-        <v>6707498.438069755</v>
+        <v>6707520</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -752,19 +746,9 @@
           <t>2021-10-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +775,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96673154</v>
+        <v>103472889</v>
       </c>
       <c r="B3" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,40 +786,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Söderåsen, Gstr</t>
+          <t>Söderåsen , Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578415.8027023608</v>
+        <v>578384</v>
       </c>
       <c r="R3" t="n">
-        <v>6707498.620362832</v>
+        <v>6707590</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,76 +861,63 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Lars-Erik Nilsson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96664545</v>
+        <v>96671785</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hofors, Gstr</t>
+          <t>Söderåsen, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578394.4684932196</v>
+        <v>578485</v>
       </c>
       <c r="R4" t="n">
-        <v>6707526.2522877</v>
+        <v>6707507</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,19 +944,14 @@
           <t>2021-10-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-15</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:10</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,33 +960,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96671785</v>
+        <v>96673154</v>
       </c>
       <c r="B5" t="n">
-        <v>89780</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,21 +990,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578484.7269526491</v>
+        <v>578416</v>
       </c>
       <c r="R5" t="n">
-        <v>6707507.509031045</v>
+        <v>6707499</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1105,48 +1050,579 @@
           <t>2021-10-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>96664535</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hofors, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>578383</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6707537</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>96664545</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hofors, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>578395</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6707526</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>96673048</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Söderåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>578378</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6707544</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>96673163</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Söderåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>578430</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6707498</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>96955687</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hofors, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>578390</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6707542</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-11-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-11-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>John Lindström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>John Lindström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
